--- a/artfynd/A 48227-2023 artfynd.xlsx
+++ b/artfynd/A 48227-2023 artfynd.xlsx
@@ -1041,10 +1041,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113188901</v>
+        <v>113188839</v>
       </c>
       <c r="B5" t="n">
-        <v>90043</v>
+        <v>56765</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1057,34 +1057,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>545248</v>
+        <v>545382</v>
       </c>
       <c r="R5" t="n">
-        <v>7206405</v>
+        <v>7206546</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1116,7 +1121,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1126,7 +1131,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1153,10 +1158,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113188838</v>
+        <v>113188925</v>
       </c>
       <c r="B6" t="n">
-        <v>56765</v>
+        <v>78121</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1169,39 +1174,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>545382</v>
+        <v>545248</v>
       </c>
       <c r="R6" t="n">
-        <v>7206578</v>
+        <v>7206407</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1233,7 +1233,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1270,10 +1270,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113188853</v>
+        <v>113188926</v>
       </c>
       <c r="B7" t="n">
-        <v>78186</v>
+        <v>78121</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1286,21 +1286,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1310,10 +1310,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>545268</v>
+        <v>545232</v>
       </c>
       <c r="R7" t="n">
-        <v>7206396</v>
+        <v>7206434</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1345,7 +1345,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1355,7 +1355,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1382,10 +1382,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113188922</v>
+        <v>113188850</v>
       </c>
       <c r="B8" t="n">
-        <v>78105</v>
+        <v>77102</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1398,21 +1398,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1422,10 +1422,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>545267</v>
+        <v>545274</v>
       </c>
       <c r="R8" t="n">
-        <v>7206397</v>
+        <v>7206405</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1457,7 +1457,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1494,10 +1494,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113188924</v>
+        <v>113188848</v>
       </c>
       <c r="B9" t="n">
-        <v>78105</v>
+        <v>74307</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1510,21 +1510,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>1467</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1534,10 +1534,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>545265</v>
+        <v>545291</v>
       </c>
       <c r="R9" t="n">
-        <v>7206396</v>
+        <v>7206429</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1569,7 +1569,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1579,7 +1579,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1606,10 +1606,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113188925</v>
+        <v>113188922</v>
       </c>
       <c r="B10" t="n">
-        <v>78105</v>
+        <v>78121</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1646,10 +1646,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>545248</v>
+        <v>545267</v>
       </c>
       <c r="R10" t="n">
-        <v>7206407</v>
+        <v>7206397</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1681,7 +1681,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1691,7 +1691,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1718,10 +1718,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113188850</v>
+        <v>113188835</v>
       </c>
       <c r="B11" t="n">
-        <v>77086</v>
+        <v>74302</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1734,21 +1734,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228579</v>
+        <v>6440</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1761,7 +1761,7 @@
         <v>545274</v>
       </c>
       <c r="R11" t="n">
-        <v>7206405</v>
+        <v>7206404</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1830,10 +1830,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113188919</v>
+        <v>113188837</v>
       </c>
       <c r="B12" t="n">
-        <v>78105</v>
+        <v>90727</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1842,25 +1842,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1870,10 +1870,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>545290</v>
+        <v>545361</v>
       </c>
       <c r="R12" t="n">
-        <v>7206432</v>
+        <v>7206519</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1905,7 +1905,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1915,7 +1915,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1942,10 +1942,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113188852</v>
+        <v>113188901</v>
       </c>
       <c r="B13" t="n">
-        <v>56872</v>
+        <v>90059</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1954,42 +1954,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103031</v>
+        <v>1204</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>545348</v>
+        <v>545248</v>
       </c>
       <c r="R13" t="n">
-        <v>7206503</v>
+        <v>7206405</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2021,7 +2017,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2031,7 +2027,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2058,10 +2054,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113188843</v>
+        <v>113188851</v>
       </c>
       <c r="B14" t="n">
-        <v>56781</v>
+        <v>77478</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2070,40 +2066,35 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>498</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>545262</v>
+        <v>545263</v>
       </c>
       <c r="R14" t="n">
         <v>7206397</v>
@@ -2175,10 +2166,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113188916</v>
+        <v>113188917</v>
       </c>
       <c r="B15" t="n">
-        <v>78105</v>
+        <v>78121</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2215,10 +2206,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>545387</v>
+        <v>545351</v>
       </c>
       <c r="R15" t="n">
-        <v>7206545</v>
+        <v>7206502</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2250,7 +2241,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2260,7 +2251,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2403,10 +2394,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113188917</v>
+        <v>113188916</v>
       </c>
       <c r="B17" t="n">
-        <v>78105</v>
+        <v>78121</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2443,10 +2434,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>545351</v>
+        <v>545387</v>
       </c>
       <c r="R17" t="n">
-        <v>7206502</v>
+        <v>7206545</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2478,7 +2469,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2488,7 +2479,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2515,10 +2506,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113188839</v>
+        <v>113188921</v>
       </c>
       <c r="B18" t="n">
-        <v>56765</v>
+        <v>78121</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2531,39 +2522,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>545382</v>
+        <v>545269</v>
       </c>
       <c r="R18" t="n">
-        <v>7206546</v>
+        <v>7206387</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2595,7 +2581,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2605,7 +2591,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2632,10 +2618,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113188926</v>
+        <v>113188843</v>
       </c>
       <c r="B19" t="n">
-        <v>78105</v>
+        <v>56781</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2648,34 +2634,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>545232</v>
+        <v>545262</v>
       </c>
       <c r="R19" t="n">
-        <v>7206434</v>
+        <v>7206397</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2707,7 +2698,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2717,7 +2708,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2744,10 +2735,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113188921</v>
+        <v>113188918</v>
       </c>
       <c r="B20" t="n">
-        <v>78105</v>
+        <v>78121</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2784,10 +2775,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>545269</v>
+        <v>545336</v>
       </c>
       <c r="R20" t="n">
-        <v>7206387</v>
+        <v>7206471</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2819,7 +2810,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2829,7 +2820,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2856,10 +2847,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113188918</v>
+        <v>113188924</v>
       </c>
       <c r="B21" t="n">
-        <v>78105</v>
+        <v>78121</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2896,10 +2887,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>545336</v>
+        <v>545265</v>
       </c>
       <c r="R21" t="n">
-        <v>7206471</v>
+        <v>7206396</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2931,7 +2922,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2941,7 +2932,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2971,7 +2962,7 @@
         <v>113188920</v>
       </c>
       <c r="B22" t="n">
-        <v>78105</v>
+        <v>78121</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3080,10 +3071,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113188851</v>
+        <v>113188852</v>
       </c>
       <c r="B23" t="n">
-        <v>77462</v>
+        <v>56872</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3092,38 +3083,42 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>498</v>
+        <v>103031</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>545263</v>
+        <v>545348</v>
       </c>
       <c r="R23" t="n">
-        <v>7206397</v>
+        <v>7206503</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3155,7 +3150,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3165,7 +3160,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3192,10 +3187,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>113188848</v>
+        <v>113188853</v>
       </c>
       <c r="B24" t="n">
-        <v>74291</v>
+        <v>78202</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3208,21 +3203,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1467</v>
+        <v>864</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3232,10 +3227,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>545291</v>
+        <v>545268</v>
       </c>
       <c r="R24" t="n">
-        <v>7206429</v>
+        <v>7206396</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3267,7 +3262,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3277,7 +3272,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3304,10 +3299,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>113188837</v>
+        <v>113188919</v>
       </c>
       <c r="B25" t="n">
-        <v>90711</v>
+        <v>78121</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3316,25 +3311,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3344,10 +3339,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>545361</v>
+        <v>545290</v>
       </c>
       <c r="R25" t="n">
-        <v>7206519</v>
+        <v>7206432</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3379,7 +3374,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3389,7 +3384,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3416,10 +3411,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>113188835</v>
+        <v>113188838</v>
       </c>
       <c r="B26" t="n">
-        <v>74286</v>
+        <v>56765</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3432,34 +3427,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>545274</v>
+        <v>545382</v>
       </c>
       <c r="R26" t="n">
-        <v>7206404</v>
+        <v>7206578</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3491,7 +3491,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3501,7 +3501,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD26" t="b">

--- a/artfynd/A 48227-2023 artfynd.xlsx
+++ b/artfynd/A 48227-2023 artfynd.xlsx
@@ -2847,7 +2847,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113188924</v>
+        <v>113188920</v>
       </c>
       <c r="B21" t="n">
         <v>78121</v>
@@ -2887,10 +2887,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>545265</v>
+        <v>545275</v>
       </c>
       <c r="R21" t="n">
-        <v>7206396</v>
+        <v>7206403</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2922,7 +2922,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2932,7 +2932,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2959,7 +2959,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113188920</v>
+        <v>113188924</v>
       </c>
       <c r="B22" t="n">
         <v>78121</v>
@@ -2999,10 +2999,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>545275</v>
+        <v>545265</v>
       </c>
       <c r="R22" t="n">
-        <v>7206403</v>
+        <v>7206396</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3034,7 +3034,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3044,7 +3044,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD22" t="b">

--- a/artfynd/A 48227-2023 artfynd.xlsx
+++ b/artfynd/A 48227-2023 artfynd.xlsx
@@ -1041,10 +1041,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113188839</v>
+        <v>113188851</v>
       </c>
       <c r="B5" t="n">
-        <v>56765</v>
+        <v>77478</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1053,43 +1053,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>498</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>545382</v>
+        <v>545263</v>
       </c>
       <c r="R5" t="n">
-        <v>7206546</v>
+        <v>7206397</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1121,7 +1116,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1131,7 +1126,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1158,7 +1153,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113188925</v>
+        <v>113188924</v>
       </c>
       <c r="B6" t="n">
         <v>78121</v>
@@ -1198,10 +1193,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>545248</v>
+        <v>545265</v>
       </c>
       <c r="R6" t="n">
-        <v>7206407</v>
+        <v>7206396</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1233,7 +1228,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1243,7 +1238,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1270,10 +1265,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113188926</v>
+        <v>113188848</v>
       </c>
       <c r="B7" t="n">
-        <v>78121</v>
+        <v>74307</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1286,21 +1281,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>1467</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1310,10 +1305,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>545232</v>
+        <v>545291</v>
       </c>
       <c r="R7" t="n">
-        <v>7206434</v>
+        <v>7206429</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1345,7 +1340,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1355,7 +1350,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1382,10 +1377,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113188850</v>
+        <v>113188920</v>
       </c>
       <c r="B8" t="n">
-        <v>77102</v>
+        <v>78121</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1398,21 +1393,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1422,10 +1417,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>545274</v>
+        <v>545275</v>
       </c>
       <c r="R8" t="n">
-        <v>7206405</v>
+        <v>7206403</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1494,10 +1489,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113188848</v>
+        <v>113188926</v>
       </c>
       <c r="B9" t="n">
-        <v>74307</v>
+        <v>78121</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1510,21 +1505,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1467</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1534,10 +1529,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>545291</v>
+        <v>545232</v>
       </c>
       <c r="R9" t="n">
-        <v>7206429</v>
+        <v>7206434</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1569,7 +1564,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1579,7 +1574,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1606,7 +1601,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113188922</v>
+        <v>113188919</v>
       </c>
       <c r="B10" t="n">
         <v>78121</v>
@@ -1646,10 +1641,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>545267</v>
+        <v>545290</v>
       </c>
       <c r="R10" t="n">
-        <v>7206397</v>
+        <v>7206432</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1681,7 +1676,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1691,7 +1686,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1718,10 +1713,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113188835</v>
+        <v>113188925</v>
       </c>
       <c r="B11" t="n">
-        <v>74302</v>
+        <v>78121</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1734,21 +1729,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1758,10 +1753,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>545274</v>
+        <v>545248</v>
       </c>
       <c r="R11" t="n">
-        <v>7206404</v>
+        <v>7206407</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1793,7 +1788,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1803,7 +1798,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1830,10 +1825,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113188837</v>
+        <v>113188841</v>
       </c>
       <c r="B12" t="n">
-        <v>90727</v>
+        <v>56910</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1842,38 +1837,42 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>3298</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>545361</v>
+        <v>545269</v>
       </c>
       <c r="R12" t="n">
-        <v>7206519</v>
+        <v>7206387</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1905,7 +1904,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1915,7 +1914,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1942,10 +1941,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113188901</v>
+        <v>113188838</v>
       </c>
       <c r="B13" t="n">
-        <v>90059</v>
+        <v>56765</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1958,34 +1957,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>545248</v>
+        <v>545382</v>
       </c>
       <c r="R13" t="n">
-        <v>7206405</v>
+        <v>7206578</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2017,7 +2021,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2027,7 +2031,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2054,10 +2058,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113188851</v>
+        <v>113188835</v>
       </c>
       <c r="B14" t="n">
-        <v>77478</v>
+        <v>74302</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2066,25 +2070,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>498</v>
+        <v>6440</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2094,10 +2098,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>545263</v>
+        <v>545274</v>
       </c>
       <c r="R14" t="n">
-        <v>7206397</v>
+        <v>7206404</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2129,7 +2133,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2139,7 +2143,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2166,7 +2170,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113188917</v>
+        <v>113188918</v>
       </c>
       <c r="B15" t="n">
         <v>78121</v>
@@ -2206,10 +2210,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>545351</v>
+        <v>545336</v>
       </c>
       <c r="R15" t="n">
-        <v>7206502</v>
+        <v>7206471</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2241,7 +2245,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2251,7 +2255,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2278,10 +2282,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113188841</v>
+        <v>113188853</v>
       </c>
       <c r="B16" t="n">
-        <v>56910</v>
+        <v>78202</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2294,38 +2298,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>864</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Lynge) Ahti</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>545269</v>
+        <v>545268</v>
       </c>
       <c r="R16" t="n">
-        <v>7206387</v>
+        <v>7206396</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2357,7 +2357,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2367,7 +2367,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2506,10 +2506,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113188921</v>
+        <v>113188837</v>
       </c>
       <c r="B18" t="n">
-        <v>78121</v>
+        <v>90727</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2518,25 +2518,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2546,10 +2546,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>545269</v>
+        <v>545361</v>
       </c>
       <c r="R18" t="n">
-        <v>7206387</v>
+        <v>7206519</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2581,7 +2581,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2618,10 +2618,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113188843</v>
+        <v>113188922</v>
       </c>
       <c r="B19" t="n">
-        <v>56781</v>
+        <v>78121</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2634,36 +2634,31 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>545262</v>
+        <v>545267</v>
       </c>
       <c r="R19" t="n">
         <v>7206397</v>
@@ -2698,7 +2693,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2708,7 +2703,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2735,7 +2730,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113188918</v>
+        <v>113188921</v>
       </c>
       <c r="B20" t="n">
         <v>78121</v>
@@ -2775,10 +2770,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>545336</v>
+        <v>545269</v>
       </c>
       <c r="R20" t="n">
-        <v>7206471</v>
+        <v>7206387</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2810,7 +2805,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2820,7 +2815,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2847,10 +2842,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113188920</v>
+        <v>113188901</v>
       </c>
       <c r="B21" t="n">
-        <v>78121</v>
+        <v>90059</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2863,21 +2858,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2887,10 +2882,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>545275</v>
+        <v>545248</v>
       </c>
       <c r="R21" t="n">
-        <v>7206403</v>
+        <v>7206405</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2922,7 +2917,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2932,7 +2927,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2959,7 +2954,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113188924</v>
+        <v>113188917</v>
       </c>
       <c r="B22" t="n">
         <v>78121</v>
@@ -2999,10 +2994,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>545265</v>
+        <v>545351</v>
       </c>
       <c r="R22" t="n">
-        <v>7206396</v>
+        <v>7206502</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3034,7 +3029,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3044,7 +3039,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3071,10 +3066,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113188852</v>
+        <v>113188839</v>
       </c>
       <c r="B23" t="n">
-        <v>56872</v>
+        <v>56765</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3083,20 +3078,20 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -3104,9 +3099,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>2</t>
+      <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3115,10 +3111,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>545348</v>
+        <v>545382</v>
       </c>
       <c r="R23" t="n">
-        <v>7206503</v>
+        <v>7206546</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3150,7 +3146,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3160,7 +3156,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3187,10 +3183,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>113188853</v>
+        <v>113188850</v>
       </c>
       <c r="B24" t="n">
-        <v>78202</v>
+        <v>77102</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3203,21 +3199,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>864</v>
+        <v>228579</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3227,10 +3223,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>545268</v>
+        <v>545274</v>
       </c>
       <c r="R24" t="n">
-        <v>7206396</v>
+        <v>7206405</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3262,7 +3258,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3272,7 +3268,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3299,10 +3295,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>113188919</v>
+        <v>113188843</v>
       </c>
       <c r="B25" t="n">
-        <v>78121</v>
+        <v>56781</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3315,34 +3311,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>545290</v>
+        <v>545262</v>
       </c>
       <c r="R25" t="n">
-        <v>7206432</v>
+        <v>7206397</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3374,7 +3375,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3384,7 +3385,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3411,10 +3412,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>113188838</v>
+        <v>113188852</v>
       </c>
       <c r="B26" t="n">
-        <v>56765</v>
+        <v>56872</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3423,20 +3424,20 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3444,10 +3445,9 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3456,10 +3456,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>545382</v>
+        <v>545348</v>
       </c>
       <c r="R26" t="n">
-        <v>7206578</v>
+        <v>7206503</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3491,7 +3491,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3501,7 +3501,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD26" t="b">

--- a/artfynd/A 48227-2023 artfynd.xlsx
+++ b/artfynd/A 48227-2023 artfynd.xlsx
@@ -1041,10 +1041,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113188851</v>
+        <v>113188835</v>
       </c>
       <c r="B5" t="n">
-        <v>77478</v>
+        <v>74314</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1053,25 +1053,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>498</v>
+        <v>6440</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1081,10 +1081,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>545263</v>
+        <v>545274</v>
       </c>
       <c r="R5" t="n">
-        <v>7206397</v>
+        <v>7206404</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1116,7 +1116,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1153,10 +1153,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113188924</v>
+        <v>113188850</v>
       </c>
       <c r="B6" t="n">
-        <v>78121</v>
+        <v>77114</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1169,21 +1169,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1193,10 +1193,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>545265</v>
+        <v>545274</v>
       </c>
       <c r="R6" t="n">
-        <v>7206396</v>
+        <v>7206405</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1228,7 +1228,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1268,7 +1268,7 @@
         <v>113188848</v>
       </c>
       <c r="B7" t="n">
-        <v>74307</v>
+        <v>74319</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1377,10 +1377,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113188920</v>
+        <v>113188916</v>
       </c>
       <c r="B8" t="n">
-        <v>78121</v>
+        <v>78133</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1417,10 +1417,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>545275</v>
+        <v>545387</v>
       </c>
       <c r="R8" t="n">
-        <v>7206403</v>
+        <v>7206545</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1462,7 +1462,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1489,10 +1489,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113188926</v>
+        <v>113188917</v>
       </c>
       <c r="B9" t="n">
-        <v>78121</v>
+        <v>78133</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1529,10 +1529,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>545232</v>
+        <v>545351</v>
       </c>
       <c r="R9" t="n">
-        <v>7206434</v>
+        <v>7206502</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1574,7 +1574,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1601,10 +1601,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113188919</v>
+        <v>113188920</v>
       </c>
       <c r="B10" t="n">
-        <v>78121</v>
+        <v>78133</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1641,10 +1641,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>545290</v>
+        <v>545275</v>
       </c>
       <c r="R10" t="n">
-        <v>7206432</v>
+        <v>7206403</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1676,7 +1676,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1713,10 +1713,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113188925</v>
+        <v>113188919</v>
       </c>
       <c r="B11" t="n">
-        <v>78121</v>
+        <v>78133</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1753,10 +1753,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>545248</v>
+        <v>545290</v>
       </c>
       <c r="R11" t="n">
-        <v>7206407</v>
+        <v>7206432</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1788,7 +1788,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1798,7 +1798,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1825,10 +1825,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113188841</v>
+        <v>113188925</v>
       </c>
       <c r="B12" t="n">
-        <v>56910</v>
+        <v>78133</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1841,38 +1841,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>545269</v>
+        <v>545248</v>
       </c>
       <c r="R12" t="n">
-        <v>7206387</v>
+        <v>7206407</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1904,7 +1900,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1914,7 +1910,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1941,10 +1937,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113188838</v>
+        <v>113188839</v>
       </c>
       <c r="B13" t="n">
-        <v>56765</v>
+        <v>56766</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1989,7 +1985,7 @@
         <v>545382</v>
       </c>
       <c r="R13" t="n">
-        <v>7206578</v>
+        <v>7206546</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2021,7 +2017,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2031,7 +2027,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2058,10 +2054,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113188835</v>
+        <v>113188922</v>
       </c>
       <c r="B14" t="n">
-        <v>74302</v>
+        <v>78133</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2074,21 +2070,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2098,10 +2094,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>545274</v>
+        <v>545267</v>
       </c>
       <c r="R14" t="n">
-        <v>7206404</v>
+        <v>7206397</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2133,7 +2129,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2143,7 +2139,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2170,10 +2166,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113188918</v>
+        <v>113188901</v>
       </c>
       <c r="B15" t="n">
-        <v>78121</v>
+        <v>90071</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2186,21 +2182,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2210,10 +2206,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>545336</v>
+        <v>545248</v>
       </c>
       <c r="R15" t="n">
-        <v>7206471</v>
+        <v>7206405</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2245,7 +2241,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2255,7 +2251,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2285,7 +2281,7 @@
         <v>113188853</v>
       </c>
       <c r="B16" t="n">
-        <v>78202</v>
+        <v>78214</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2394,10 +2390,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113188916</v>
+        <v>113188924</v>
       </c>
       <c r="B17" t="n">
-        <v>78121</v>
+        <v>78133</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2434,10 +2430,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>545387</v>
+        <v>545265</v>
       </c>
       <c r="R17" t="n">
-        <v>7206545</v>
+        <v>7206396</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2469,7 +2465,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2479,7 +2475,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2506,10 +2502,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113188837</v>
+        <v>113188921</v>
       </c>
       <c r="B18" t="n">
-        <v>90727</v>
+        <v>78133</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2518,25 +2514,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2546,10 +2542,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>545361</v>
+        <v>545269</v>
       </c>
       <c r="R18" t="n">
-        <v>7206519</v>
+        <v>7206387</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2581,7 +2577,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2591,7 +2587,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2618,10 +2614,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113188922</v>
+        <v>113188837</v>
       </c>
       <c r="B19" t="n">
-        <v>78121</v>
+        <v>90739</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2630,25 +2626,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2658,10 +2654,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>545267</v>
+        <v>545361</v>
       </c>
       <c r="R19" t="n">
-        <v>7206397</v>
+        <v>7206519</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2693,7 +2689,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2703,7 +2699,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2730,10 +2726,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113188921</v>
+        <v>113188843</v>
       </c>
       <c r="B20" t="n">
-        <v>78121</v>
+        <v>56782</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2746,34 +2742,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>545269</v>
+        <v>545262</v>
       </c>
       <c r="R20" t="n">
-        <v>7206387</v>
+        <v>7206397</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2805,7 +2806,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2815,7 +2816,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2842,10 +2843,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113188901</v>
+        <v>113188852</v>
       </c>
       <c r="B21" t="n">
-        <v>90059</v>
+        <v>56873</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2854,38 +2855,42 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1204</v>
+        <v>103031</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>545248</v>
+        <v>545348</v>
       </c>
       <c r="R21" t="n">
-        <v>7206405</v>
+        <v>7206503</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2917,7 +2922,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2927,7 +2932,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2954,10 +2959,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113188917</v>
+        <v>113188918</v>
       </c>
       <c r="B22" t="n">
-        <v>78121</v>
+        <v>78133</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2994,10 +2999,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>545351</v>
+        <v>545336</v>
       </c>
       <c r="R22" t="n">
-        <v>7206502</v>
+        <v>7206471</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3029,7 +3034,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3039,7 +3044,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3066,10 +3071,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113188839</v>
+        <v>113188838</v>
       </c>
       <c r="B23" t="n">
-        <v>56765</v>
+        <v>56766</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3114,7 +3119,7 @@
         <v>545382</v>
       </c>
       <c r="R23" t="n">
-        <v>7206546</v>
+        <v>7206578</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3146,7 +3151,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3156,7 +3161,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3183,10 +3188,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>113188850</v>
+        <v>113188851</v>
       </c>
       <c r="B24" t="n">
-        <v>77102</v>
+        <v>77490</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3195,25 +3200,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228579</v>
+        <v>498</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3223,10 +3228,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>545274</v>
+        <v>545263</v>
       </c>
       <c r="R24" t="n">
-        <v>7206405</v>
+        <v>7206397</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3258,7 +3263,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3268,7 +3273,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3295,10 +3300,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>113188843</v>
+        <v>113188841</v>
       </c>
       <c r="B25" t="n">
-        <v>56781</v>
+        <v>56911</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3311,27 +3316,26 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3340,10 +3344,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>545262</v>
+        <v>545269</v>
       </c>
       <c r="R25" t="n">
-        <v>7206397</v>
+        <v>7206387</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3375,7 +3379,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3385,7 +3389,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3412,10 +3416,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>113188852</v>
+        <v>113188926</v>
       </c>
       <c r="B26" t="n">
-        <v>56872</v>
+        <v>78133</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3424,42 +3428,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>545348</v>
+        <v>545232</v>
       </c>
       <c r="R26" t="n">
-        <v>7206503</v>
+        <v>7206434</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3491,7 +3491,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3501,7 +3501,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD26" t="b">

--- a/artfynd/A 48227-2023 artfynd.xlsx
+++ b/artfynd/A 48227-2023 artfynd.xlsx
@@ -1041,10 +1041,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113188835</v>
+        <v>113188850</v>
       </c>
       <c r="B5" t="n">
-        <v>74314</v>
+        <v>77114</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1057,21 +1057,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6440</v>
+        <v>228579</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1084,7 +1084,7 @@
         <v>545274</v>
       </c>
       <c r="R5" t="n">
-        <v>7206404</v>
+        <v>7206405</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1153,10 +1153,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113188850</v>
+        <v>113188920</v>
       </c>
       <c r="B6" t="n">
-        <v>77114</v>
+        <v>78133</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1169,21 +1169,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1193,10 +1193,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>545274</v>
+        <v>545275</v>
       </c>
       <c r="R6" t="n">
-        <v>7206405</v>
+        <v>7206403</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1265,10 +1265,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113188848</v>
+        <v>113188901</v>
       </c>
       <c r="B7" t="n">
-        <v>74319</v>
+        <v>90071</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1281,21 +1281,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1467</v>
+        <v>1204</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1305,10 +1305,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>545291</v>
+        <v>545248</v>
       </c>
       <c r="R7" t="n">
-        <v>7206429</v>
+        <v>7206405</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1340,7 +1340,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1350,7 +1350,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1377,7 +1377,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113188916</v>
+        <v>113188926</v>
       </c>
       <c r="B8" t="n">
         <v>78133</v>
@@ -1417,10 +1417,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>545387</v>
+        <v>545232</v>
       </c>
       <c r="R8" t="n">
-        <v>7206545</v>
+        <v>7206434</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1462,7 +1462,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1489,10 +1489,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113188917</v>
+        <v>113188837</v>
       </c>
       <c r="B9" t="n">
-        <v>78133</v>
+        <v>90739</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1501,25 +1501,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1529,10 +1529,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>545351</v>
+        <v>545361</v>
       </c>
       <c r="R9" t="n">
-        <v>7206502</v>
+        <v>7206519</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1601,7 +1601,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113188920</v>
+        <v>113188921</v>
       </c>
       <c r="B10" t="n">
         <v>78133</v>
@@ -1641,10 +1641,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>545275</v>
+        <v>545269</v>
       </c>
       <c r="R10" t="n">
-        <v>7206403</v>
+        <v>7206387</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1676,7 +1676,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1825,7 +1825,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113188925</v>
+        <v>113188917</v>
       </c>
       <c r="B12" t="n">
         <v>78133</v>
@@ -1865,10 +1865,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>545248</v>
+        <v>545351</v>
       </c>
       <c r="R12" t="n">
-        <v>7206407</v>
+        <v>7206502</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1900,7 +1900,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1937,10 +1937,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113188839</v>
+        <v>113188925</v>
       </c>
       <c r="B13" t="n">
-        <v>56766</v>
+        <v>78133</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1953,39 +1953,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>545382</v>
+        <v>545248</v>
       </c>
       <c r="R13" t="n">
-        <v>7206546</v>
+        <v>7206407</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2017,7 +2012,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2027,7 +2022,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2054,10 +2049,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113188922</v>
+        <v>113188838</v>
       </c>
       <c r="B14" t="n">
-        <v>78133</v>
+        <v>56766</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2070,34 +2065,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>545267</v>
+        <v>545382</v>
       </c>
       <c r="R14" t="n">
-        <v>7206397</v>
+        <v>7206578</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2129,7 +2129,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2139,7 +2139,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2166,10 +2166,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113188901</v>
+        <v>113188922</v>
       </c>
       <c r="B15" t="n">
-        <v>90071</v>
+        <v>78133</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2182,21 +2182,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2206,10 +2206,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>545248</v>
+        <v>545267</v>
       </c>
       <c r="R15" t="n">
-        <v>7206405</v>
+        <v>7206397</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2241,7 +2241,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2251,7 +2251,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2390,10 +2390,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113188924</v>
+        <v>113188848</v>
       </c>
       <c r="B17" t="n">
-        <v>78133</v>
+        <v>74319</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2406,21 +2406,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>1467</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2430,10 +2430,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>545265</v>
+        <v>545291</v>
       </c>
       <c r="R17" t="n">
-        <v>7206396</v>
+        <v>7206429</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2465,7 +2465,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2475,7 +2475,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2502,7 +2502,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113188921</v>
+        <v>113188916</v>
       </c>
       <c r="B18" t="n">
         <v>78133</v>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>545269</v>
+        <v>545387</v>
       </c>
       <c r="R18" t="n">
-        <v>7206387</v>
+        <v>7206545</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2577,7 +2577,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2587,7 +2587,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2614,10 +2614,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113188837</v>
+        <v>113188839</v>
       </c>
       <c r="B19" t="n">
-        <v>90739</v>
+        <v>56766</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2626,38 +2626,43 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>545361</v>
+        <v>545382</v>
       </c>
       <c r="R19" t="n">
-        <v>7206519</v>
+        <v>7206546</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2689,7 +2694,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2699,7 +2704,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2726,10 +2731,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113188843</v>
+        <v>113188851</v>
       </c>
       <c r="B20" t="n">
-        <v>56782</v>
+        <v>77490</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2738,40 +2743,35 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>498</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>545262</v>
+        <v>545263</v>
       </c>
       <c r="R20" t="n">
         <v>7206397</v>
@@ -2843,10 +2843,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113188852</v>
+        <v>113188835</v>
       </c>
       <c r="B21" t="n">
-        <v>56873</v>
+        <v>74314</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2855,42 +2855,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103031</v>
+        <v>6440</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>545348</v>
+        <v>545274</v>
       </c>
       <c r="R21" t="n">
-        <v>7206503</v>
+        <v>7206404</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2922,7 +2918,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2932,7 +2928,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2959,10 +2955,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113188918</v>
+        <v>113188852</v>
       </c>
       <c r="B22" t="n">
-        <v>78133</v>
+        <v>56873</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2971,38 +2967,42 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>545336</v>
+        <v>545348</v>
       </c>
       <c r="R22" t="n">
-        <v>7206471</v>
+        <v>7206503</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3034,7 +3034,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3044,7 +3044,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3071,10 +3071,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113188838</v>
+        <v>113188924</v>
       </c>
       <c r="B23" t="n">
-        <v>56766</v>
+        <v>78133</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3087,39 +3087,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>545382</v>
+        <v>545265</v>
       </c>
       <c r="R23" t="n">
-        <v>7206578</v>
+        <v>7206396</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3151,7 +3146,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3161,7 +3156,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3188,10 +3183,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>113188851</v>
+        <v>113188843</v>
       </c>
       <c r="B24" t="n">
-        <v>77490</v>
+        <v>56782</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3200,35 +3195,40 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>498</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>545263</v>
+        <v>545262</v>
       </c>
       <c r="R24" t="n">
         <v>7206397</v>
@@ -3416,7 +3416,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>113188926</v>
+        <v>113188918</v>
       </c>
       <c r="B26" t="n">
         <v>78133</v>
@@ -3456,10 +3456,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>545232</v>
+        <v>545336</v>
       </c>
       <c r="R26" t="n">
-        <v>7206434</v>
+        <v>7206471</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3491,7 +3491,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3501,7 +3501,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD26" t="b">

--- a/artfynd/A 48227-2023 artfynd.xlsx
+++ b/artfynd/A 48227-2023 artfynd.xlsx
@@ -1041,10 +1041,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113188850</v>
+        <v>113188901</v>
       </c>
       <c r="B5" t="n">
-        <v>77114</v>
+        <v>90071</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1057,21 +1057,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228579</v>
+        <v>1204</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1081,7 +1081,7 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>545274</v>
+        <v>545248</v>
       </c>
       <c r="R5" t="n">
         <v>7206405</v>
@@ -1116,7 +1116,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1153,10 +1153,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113188920</v>
+        <v>113188850</v>
       </c>
       <c r="B6" t="n">
-        <v>78133</v>
+        <v>77114</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1169,21 +1169,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1193,10 +1193,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>545275</v>
+        <v>545274</v>
       </c>
       <c r="R6" t="n">
-        <v>7206403</v>
+        <v>7206405</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1265,10 +1265,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113188901</v>
+        <v>113188920</v>
       </c>
       <c r="B7" t="n">
-        <v>90071</v>
+        <v>78133</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1281,21 +1281,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1305,10 +1305,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>545248</v>
+        <v>545275</v>
       </c>
       <c r="R7" t="n">
-        <v>7206405</v>
+        <v>7206403</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1340,7 +1340,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1350,7 +1350,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1377,10 +1377,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113188926</v>
+        <v>113188837</v>
       </c>
       <c r="B8" t="n">
-        <v>78133</v>
+        <v>90739</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1389,25 +1389,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1417,10 +1417,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>545232</v>
+        <v>545361</v>
       </c>
       <c r="R8" t="n">
-        <v>7206434</v>
+        <v>7206519</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1462,7 +1462,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1489,10 +1489,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113188837</v>
+        <v>113188926</v>
       </c>
       <c r="B9" t="n">
-        <v>90739</v>
+        <v>78133</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1501,25 +1501,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1529,10 +1529,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>545361</v>
+        <v>545232</v>
       </c>
       <c r="R9" t="n">
-        <v>7206519</v>
+        <v>7206434</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1574,7 +1574,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -2049,10 +2049,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113188838</v>
+        <v>113188853</v>
       </c>
       <c r="B14" t="n">
-        <v>56766</v>
+        <v>78214</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2065,39 +2065,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>864</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>545382</v>
+        <v>545268</v>
       </c>
       <c r="R14" t="n">
-        <v>7206578</v>
+        <v>7206396</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2129,7 +2124,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2139,7 +2134,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2166,10 +2161,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113188922</v>
+        <v>113188838</v>
       </c>
       <c r="B15" t="n">
-        <v>78133</v>
+        <v>56766</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2182,34 +2177,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>545267</v>
+        <v>545382</v>
       </c>
       <c r="R15" t="n">
-        <v>7206397</v>
+        <v>7206578</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2241,7 +2241,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2251,7 +2251,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2278,10 +2278,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113188853</v>
+        <v>113188922</v>
       </c>
       <c r="B16" t="n">
-        <v>78214</v>
+        <v>78133</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2294,21 +2294,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2318,10 +2318,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>545268</v>
+        <v>545267</v>
       </c>
       <c r="R16" t="n">
-        <v>7206396</v>
+        <v>7206397</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>

--- a/artfynd/A 48227-2023 artfynd.xlsx
+++ b/artfynd/A 48227-2023 artfynd.xlsx
@@ -1041,10 +1041,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113188901</v>
+        <v>113188924</v>
       </c>
       <c r="B5" t="n">
-        <v>90071</v>
+        <v>78155</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1057,21 +1057,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1081,10 +1081,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>545248</v>
+        <v>545265</v>
       </c>
       <c r="R5" t="n">
-        <v>7206405</v>
+        <v>7206396</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1116,7 +1116,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1153,10 +1153,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113188850</v>
+        <v>113188926</v>
       </c>
       <c r="B6" t="n">
-        <v>77114</v>
+        <v>78155</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1169,21 +1169,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1193,10 +1193,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>545274</v>
+        <v>545232</v>
       </c>
       <c r="R6" t="n">
-        <v>7206405</v>
+        <v>7206434</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1228,7 +1228,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1265,10 +1265,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113188920</v>
+        <v>113188837</v>
       </c>
       <c r="B7" t="n">
-        <v>78133</v>
+        <v>90761</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1277,25 +1277,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1305,10 +1305,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>545275</v>
+        <v>545361</v>
       </c>
       <c r="R7" t="n">
-        <v>7206403</v>
+        <v>7206519</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1340,7 +1340,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1350,7 +1350,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1377,10 +1377,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113188837</v>
+        <v>113188916</v>
       </c>
       <c r="B8" t="n">
-        <v>90739</v>
+        <v>78155</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1389,25 +1389,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1417,10 +1417,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>545361</v>
+        <v>545387</v>
       </c>
       <c r="R8" t="n">
-        <v>7206519</v>
+        <v>7206545</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1462,7 +1462,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1489,10 +1489,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113188926</v>
+        <v>113188838</v>
       </c>
       <c r="B9" t="n">
-        <v>78133</v>
+        <v>56766</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1505,34 +1505,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>545232</v>
+        <v>545382</v>
       </c>
       <c r="R9" t="n">
-        <v>7206434</v>
+        <v>7206578</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1564,7 +1569,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1574,7 +1579,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1601,10 +1606,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113188921</v>
+        <v>113188839</v>
       </c>
       <c r="B10" t="n">
-        <v>78133</v>
+        <v>56766</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1617,34 +1622,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>545269</v>
+        <v>545382</v>
       </c>
       <c r="R10" t="n">
-        <v>7206387</v>
+        <v>7206546</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1676,7 +1686,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1686,7 +1696,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1713,10 +1723,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113188919</v>
+        <v>113188843</v>
       </c>
       <c r="B11" t="n">
-        <v>78133</v>
+        <v>56782</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1729,34 +1739,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>545290</v>
+        <v>545262</v>
       </c>
       <c r="R11" t="n">
-        <v>7206432</v>
+        <v>7206397</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1788,7 +1803,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1798,7 +1813,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1825,10 +1840,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113188917</v>
+        <v>113188921</v>
       </c>
       <c r="B12" t="n">
-        <v>78133</v>
+        <v>78155</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1865,10 +1880,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>545351</v>
+        <v>545269</v>
       </c>
       <c r="R12" t="n">
-        <v>7206502</v>
+        <v>7206387</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1900,7 +1915,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1910,7 +1925,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1937,10 +1952,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113188925</v>
+        <v>113188920</v>
       </c>
       <c r="B13" t="n">
-        <v>78133</v>
+        <v>78155</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1977,10 +1992,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>545248</v>
+        <v>545275</v>
       </c>
       <c r="R13" t="n">
-        <v>7206407</v>
+        <v>7206403</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2012,7 +2027,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2022,7 +2037,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2049,10 +2064,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113188853</v>
+        <v>113188901</v>
       </c>
       <c r="B14" t="n">
-        <v>78214</v>
+        <v>90093</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2065,21 +2080,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>864</v>
+        <v>1204</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2089,10 +2104,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>545268</v>
+        <v>545248</v>
       </c>
       <c r="R14" t="n">
-        <v>7206396</v>
+        <v>7206405</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2124,7 +2139,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2134,7 +2149,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2161,10 +2176,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113188838</v>
+        <v>113188922</v>
       </c>
       <c r="B15" t="n">
-        <v>56766</v>
+        <v>78155</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2177,39 +2192,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>545382</v>
+        <v>545267</v>
       </c>
       <c r="R15" t="n">
-        <v>7206578</v>
+        <v>7206397</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2241,7 +2251,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2251,7 +2261,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2278,10 +2288,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113188922</v>
+        <v>113188853</v>
       </c>
       <c r="B16" t="n">
-        <v>78133</v>
+        <v>78236</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2294,21 +2304,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2318,10 +2328,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>545267</v>
+        <v>545268</v>
       </c>
       <c r="R16" t="n">
-        <v>7206397</v>
+        <v>7206396</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2393,7 +2403,7 @@
         <v>113188848</v>
       </c>
       <c r="B17" t="n">
-        <v>74319</v>
+        <v>74341</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2502,10 +2512,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113188916</v>
+        <v>113188841</v>
       </c>
       <c r="B18" t="n">
-        <v>78133</v>
+        <v>56911</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2518,34 +2528,38 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>545387</v>
+        <v>545269</v>
       </c>
       <c r="R18" t="n">
-        <v>7206545</v>
+        <v>7206387</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2577,7 +2591,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2587,7 +2601,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2614,10 +2628,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113188839</v>
+        <v>113188850</v>
       </c>
       <c r="B19" t="n">
-        <v>56766</v>
+        <v>77136</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2630,39 +2644,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>228579</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>545382</v>
+        <v>545274</v>
       </c>
       <c r="R19" t="n">
-        <v>7206546</v>
+        <v>7206405</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2694,7 +2703,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2704,7 +2713,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2734,7 +2743,7 @@
         <v>113188851</v>
       </c>
       <c r="B20" t="n">
-        <v>77490</v>
+        <v>77512</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2846,7 +2855,7 @@
         <v>113188835</v>
       </c>
       <c r="B21" t="n">
-        <v>74314</v>
+        <v>74336</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3071,10 +3080,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113188924</v>
+        <v>113188925</v>
       </c>
       <c r="B23" t="n">
-        <v>78133</v>
+        <v>78155</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3111,10 +3120,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>545265</v>
+        <v>545248</v>
       </c>
       <c r="R23" t="n">
-        <v>7206396</v>
+        <v>7206407</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3146,7 +3155,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3156,7 +3165,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3183,10 +3192,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>113188843</v>
+        <v>113188918</v>
       </c>
       <c r="B24" t="n">
-        <v>56782</v>
+        <v>78155</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3199,39 +3208,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>545262</v>
+        <v>545336</v>
       </c>
       <c r="R24" t="n">
-        <v>7206397</v>
+        <v>7206471</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3263,7 +3267,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3273,7 +3277,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3300,10 +3304,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>113188841</v>
+        <v>113188917</v>
       </c>
       <c r="B25" t="n">
-        <v>56911</v>
+        <v>78155</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3316,38 +3320,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>545269</v>
+        <v>545351</v>
       </c>
       <c r="R25" t="n">
-        <v>7206387</v>
+        <v>7206502</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3379,7 +3379,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3389,7 +3389,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3416,10 +3416,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>113188918</v>
+        <v>113188919</v>
       </c>
       <c r="B26" t="n">
-        <v>78133</v>
+        <v>78155</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3456,10 +3456,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>545336</v>
+        <v>545290</v>
       </c>
       <c r="R26" t="n">
-        <v>7206471</v>
+        <v>7206432</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3491,7 +3491,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3501,7 +3501,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD26" t="b">

--- a/artfynd/A 48227-2023 artfynd.xlsx
+++ b/artfynd/A 48227-2023 artfynd.xlsx
@@ -1489,7 +1489,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113188838</v>
+        <v>113188839</v>
       </c>
       <c r="B9" t="n">
         <v>56766</v>
@@ -1537,7 +1537,7 @@
         <v>545382</v>
       </c>
       <c r="R9" t="n">
-        <v>7206578</v>
+        <v>7206546</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1569,7 +1569,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1579,7 +1579,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1606,7 +1606,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113188839</v>
+        <v>113188838</v>
       </c>
       <c r="B10" t="n">
         <v>56766</v>
@@ -1654,7 +1654,7 @@
         <v>545382</v>
       </c>
       <c r="R10" t="n">
-        <v>7206546</v>
+        <v>7206578</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1686,7 +1686,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1696,7 +1696,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 48227-2023 artfynd.xlsx
+++ b/artfynd/A 48227-2023 artfynd.xlsx
@@ -1041,10 +1041,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113188924</v>
+        <v>113188916</v>
       </c>
       <c r="B5" t="n">
-        <v>78155</v>
+        <v>78158</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1081,10 +1081,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>545265</v>
+        <v>545387</v>
       </c>
       <c r="R5" t="n">
-        <v>7206396</v>
+        <v>7206545</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1116,7 +1116,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1153,10 +1153,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113188926</v>
+        <v>113188901</v>
       </c>
       <c r="B6" t="n">
-        <v>78155</v>
+        <v>90097</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1169,21 +1169,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1193,10 +1193,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>545232</v>
+        <v>545248</v>
       </c>
       <c r="R6" t="n">
-        <v>7206434</v>
+        <v>7206405</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1228,7 +1228,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1265,10 +1265,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113188837</v>
+        <v>113188839</v>
       </c>
       <c r="B7" t="n">
-        <v>90761</v>
+        <v>56769</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1277,38 +1277,43 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>545361</v>
+        <v>545382</v>
       </c>
       <c r="R7" t="n">
-        <v>7206519</v>
+        <v>7206546</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1340,7 +1345,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1350,7 +1355,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1377,10 +1382,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113188916</v>
+        <v>113188918</v>
       </c>
       <c r="B8" t="n">
-        <v>78155</v>
+        <v>78158</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1417,10 +1422,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>545387</v>
+        <v>545336</v>
       </c>
       <c r="R8" t="n">
-        <v>7206545</v>
+        <v>7206471</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1452,7 +1457,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1462,7 +1467,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1489,10 +1494,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113188839</v>
+        <v>113188850</v>
       </c>
       <c r="B9" t="n">
-        <v>56766</v>
+        <v>77139</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1505,39 +1510,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>228579</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>545382</v>
+        <v>545274</v>
       </c>
       <c r="R9" t="n">
-        <v>7206546</v>
+        <v>7206405</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1569,7 +1569,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1579,7 +1579,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1606,10 +1606,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113188838</v>
+        <v>113188921</v>
       </c>
       <c r="B10" t="n">
-        <v>56766</v>
+        <v>78158</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1622,39 +1622,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>545382</v>
+        <v>545269</v>
       </c>
       <c r="R10" t="n">
-        <v>7206578</v>
+        <v>7206387</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1686,7 +1681,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1696,7 +1691,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1723,10 +1718,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113188843</v>
+        <v>113188837</v>
       </c>
       <c r="B11" t="n">
-        <v>56782</v>
+        <v>90765</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1735,43 +1730,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>3298</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>545262</v>
+        <v>545361</v>
       </c>
       <c r="R11" t="n">
-        <v>7206397</v>
+        <v>7206519</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1803,7 +1793,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1813,7 +1803,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1840,10 +1830,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113188921</v>
+        <v>113188835</v>
       </c>
       <c r="B12" t="n">
-        <v>78155</v>
+        <v>74339</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1856,21 +1846,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1880,10 +1870,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>545269</v>
+        <v>545274</v>
       </c>
       <c r="R12" t="n">
-        <v>7206387</v>
+        <v>7206404</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1915,7 +1905,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1925,7 +1915,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1952,10 +1942,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113188920</v>
+        <v>113188851</v>
       </c>
       <c r="B13" t="n">
-        <v>78155</v>
+        <v>77515</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1964,25 +1954,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>498</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1992,10 +1982,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>545275</v>
+        <v>545263</v>
       </c>
       <c r="R13" t="n">
-        <v>7206403</v>
+        <v>7206397</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2027,7 +2017,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2037,7 +2027,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2064,10 +2054,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113188901</v>
+        <v>113188848</v>
       </c>
       <c r="B14" t="n">
-        <v>90093</v>
+        <v>74344</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2080,21 +2070,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1204</v>
+        <v>1467</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2104,10 +2094,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>545248</v>
+        <v>545291</v>
       </c>
       <c r="R14" t="n">
-        <v>7206405</v>
+        <v>7206429</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2139,7 +2129,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2149,7 +2139,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2176,10 +2166,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113188922</v>
+        <v>113188852</v>
       </c>
       <c r="B15" t="n">
-        <v>78155</v>
+        <v>56876</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2188,38 +2178,42 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>545267</v>
+        <v>545348</v>
       </c>
       <c r="R15" t="n">
-        <v>7206397</v>
+        <v>7206503</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2251,7 +2245,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2261,7 +2255,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2288,10 +2282,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113188853</v>
+        <v>113188926</v>
       </c>
       <c r="B16" t="n">
-        <v>78236</v>
+        <v>78158</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2304,21 +2298,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2328,10 +2322,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>545268</v>
+        <v>545232</v>
       </c>
       <c r="R16" t="n">
-        <v>7206396</v>
+        <v>7206434</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2363,7 +2357,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2373,7 +2367,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2400,10 +2394,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113188848</v>
+        <v>113188919</v>
       </c>
       <c r="B17" t="n">
-        <v>74341</v>
+        <v>78158</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2416,21 +2410,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1467</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2440,10 +2434,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>545291</v>
+        <v>545290</v>
       </c>
       <c r="R17" t="n">
-        <v>7206429</v>
+        <v>7206432</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2475,7 +2469,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2485,7 +2479,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2512,10 +2506,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113188841</v>
+        <v>113188922</v>
       </c>
       <c r="B18" t="n">
-        <v>56911</v>
+        <v>78158</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2528,38 +2522,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>545269</v>
+        <v>545267</v>
       </c>
       <c r="R18" t="n">
-        <v>7206387</v>
+        <v>7206397</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2591,7 +2581,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2601,7 +2591,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2628,10 +2618,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113188850</v>
+        <v>113188924</v>
       </c>
       <c r="B19" t="n">
-        <v>77136</v>
+        <v>78158</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2644,21 +2634,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2668,10 +2658,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>545274</v>
+        <v>545265</v>
       </c>
       <c r="R19" t="n">
-        <v>7206405</v>
+        <v>7206396</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2703,7 +2693,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2713,7 +2703,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2740,10 +2730,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113188851</v>
+        <v>113188843</v>
       </c>
       <c r="B20" t="n">
-        <v>77512</v>
+        <v>56785</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2752,35 +2742,40 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>498</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>545263</v>
+        <v>545262</v>
       </c>
       <c r="R20" t="n">
         <v>7206397</v>
@@ -2852,10 +2847,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113188835</v>
+        <v>113188920</v>
       </c>
       <c r="B21" t="n">
-        <v>74336</v>
+        <v>78158</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2868,21 +2863,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2892,10 +2887,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>545274</v>
+        <v>545275</v>
       </c>
       <c r="R21" t="n">
-        <v>7206404</v>
+        <v>7206403</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2964,10 +2959,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113188852</v>
+        <v>113188841</v>
       </c>
       <c r="B22" t="n">
-        <v>56873</v>
+        <v>56914</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2976,30 +2971,30 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103031</v>
+        <v>103021</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3008,10 +3003,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>545348</v>
+        <v>545269</v>
       </c>
       <c r="R22" t="n">
-        <v>7206503</v>
+        <v>7206387</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3043,7 +3038,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3053,7 +3048,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3080,10 +3075,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113188925</v>
+        <v>113188838</v>
       </c>
       <c r="B23" t="n">
-        <v>78155</v>
+        <v>56769</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3096,34 +3091,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>545248</v>
+        <v>545382</v>
       </c>
       <c r="R23" t="n">
-        <v>7206407</v>
+        <v>7206578</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3155,7 +3155,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3165,7 +3165,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3192,10 +3192,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>113188918</v>
+        <v>113188853</v>
       </c>
       <c r="B24" t="n">
-        <v>78155</v>
+        <v>78240</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3208,21 +3208,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3232,10 +3232,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>545336</v>
+        <v>545268</v>
       </c>
       <c r="R24" t="n">
-        <v>7206471</v>
+        <v>7206396</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3267,7 +3267,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3277,7 +3277,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3304,10 +3304,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>113188917</v>
+        <v>113188925</v>
       </c>
       <c r="B25" t="n">
-        <v>78155</v>
+        <v>78158</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3344,10 +3344,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>545351</v>
+        <v>545248</v>
       </c>
       <c r="R25" t="n">
-        <v>7206502</v>
+        <v>7206407</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3379,7 +3379,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3389,7 +3389,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3416,10 +3416,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>113188919</v>
+        <v>113188917</v>
       </c>
       <c r="B26" t="n">
-        <v>78155</v>
+        <v>78158</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3456,10 +3456,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>545290</v>
+        <v>545351</v>
       </c>
       <c r="R26" t="n">
-        <v>7206432</v>
+        <v>7206502</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3491,7 +3491,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3501,7 +3501,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD26" t="b">

--- a/artfynd/A 48227-2023 artfynd.xlsx
+++ b/artfynd/A 48227-2023 artfynd.xlsx
@@ -1041,10 +1041,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113188916</v>
+        <v>113188901</v>
       </c>
       <c r="B5" t="n">
-        <v>78158</v>
+        <v>90097</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1057,21 +1057,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1081,10 +1081,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>545387</v>
+        <v>545248</v>
       </c>
       <c r="R5" t="n">
-        <v>7206545</v>
+        <v>7206405</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1116,7 +1116,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1153,10 +1153,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113188901</v>
+        <v>113188916</v>
       </c>
       <c r="B6" t="n">
-        <v>90097</v>
+        <v>78158</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1169,21 +1169,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1193,10 +1193,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>545248</v>
+        <v>545387</v>
       </c>
       <c r="R6" t="n">
-        <v>7206405</v>
+        <v>7206545</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1228,7 +1228,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 48227-2023 artfynd.xlsx
+++ b/artfynd/A 48227-2023 artfynd.xlsx
@@ -1041,10 +1041,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113188901</v>
+        <v>113188851</v>
       </c>
       <c r="B5" t="n">
-        <v>90097</v>
+        <v>77521</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1053,25 +1053,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1204</v>
+        <v>498</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1081,10 +1081,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>545248</v>
+        <v>545263</v>
       </c>
       <c r="R5" t="n">
-        <v>7206405</v>
+        <v>7206397</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1116,7 +1116,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1153,10 +1153,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113188916</v>
+        <v>113188918</v>
       </c>
       <c r="B6" t="n">
-        <v>78158</v>
+        <v>78164</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1193,10 +1193,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>545387</v>
+        <v>545336</v>
       </c>
       <c r="R6" t="n">
-        <v>7206545</v>
+        <v>7206471</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1228,7 +1228,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1265,10 +1265,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113188839</v>
+        <v>113188922</v>
       </c>
       <c r="B7" t="n">
-        <v>56769</v>
+        <v>78164</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1281,39 +1281,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>545382</v>
+        <v>545267</v>
       </c>
       <c r="R7" t="n">
-        <v>7206546</v>
+        <v>7206397</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1345,7 +1340,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1355,7 +1350,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1382,10 +1377,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113188918</v>
+        <v>113188838</v>
       </c>
       <c r="B8" t="n">
-        <v>78158</v>
+        <v>56773</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1398,34 +1393,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>545336</v>
+        <v>545382</v>
       </c>
       <c r="R8" t="n">
-        <v>7206471</v>
+        <v>7206578</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1457,7 +1457,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1497,7 +1497,7 @@
         <v>113188850</v>
       </c>
       <c r="B9" t="n">
-        <v>77139</v>
+        <v>77145</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1606,10 +1606,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113188921</v>
+        <v>113188843</v>
       </c>
       <c r="B10" t="n">
-        <v>78158</v>
+        <v>56789</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1622,34 +1622,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>545269</v>
+        <v>545262</v>
       </c>
       <c r="R10" t="n">
-        <v>7206387</v>
+        <v>7206397</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1681,7 +1686,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1691,7 +1696,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1718,10 +1723,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113188837</v>
+        <v>113188926</v>
       </c>
       <c r="B11" t="n">
-        <v>90765</v>
+        <v>78164</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1730,25 +1735,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1758,10 +1763,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>545361</v>
+        <v>545232</v>
       </c>
       <c r="R11" t="n">
-        <v>7206519</v>
+        <v>7206434</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1793,7 +1798,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1803,7 +1808,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1830,10 +1835,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113188835</v>
+        <v>113188901</v>
       </c>
       <c r="B12" t="n">
-        <v>74339</v>
+        <v>90103</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1846,21 +1851,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6440</v>
+        <v>1204</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1870,10 +1875,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>545274</v>
+        <v>545248</v>
       </c>
       <c r="R12" t="n">
-        <v>7206404</v>
+        <v>7206405</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1905,7 +1910,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1915,7 +1920,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1942,10 +1947,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113188851</v>
+        <v>113188853</v>
       </c>
       <c r="B13" t="n">
-        <v>77515</v>
+        <v>78246</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1954,25 +1959,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>498</v>
+        <v>864</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1982,10 +1987,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>545263</v>
+        <v>545268</v>
       </c>
       <c r="R13" t="n">
-        <v>7206397</v>
+        <v>7206396</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2017,7 +2022,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2027,7 +2032,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2054,10 +2059,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113188848</v>
+        <v>113188919</v>
       </c>
       <c r="B14" t="n">
-        <v>74344</v>
+        <v>78164</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2070,21 +2075,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1467</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2094,10 +2099,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>545291</v>
+        <v>545290</v>
       </c>
       <c r="R14" t="n">
-        <v>7206429</v>
+        <v>7206432</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2129,7 +2134,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2139,7 +2144,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2166,10 +2171,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113188852</v>
+        <v>113188837</v>
       </c>
       <c r="B15" t="n">
-        <v>56876</v>
+        <v>90771</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2182,38 +2187,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103031</v>
+        <v>3298</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>545348</v>
+        <v>545361</v>
       </c>
       <c r="R15" t="n">
-        <v>7206503</v>
+        <v>7206519</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2245,7 +2246,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2255,7 +2256,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2282,10 +2283,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113188926</v>
+        <v>113188921</v>
       </c>
       <c r="B16" t="n">
-        <v>78158</v>
+        <v>78164</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2322,10 +2323,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>545232</v>
+        <v>545269</v>
       </c>
       <c r="R16" t="n">
-        <v>7206434</v>
+        <v>7206387</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2357,7 +2358,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2367,7 +2368,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2394,10 +2395,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113188919</v>
+        <v>113188920</v>
       </c>
       <c r="B17" t="n">
-        <v>78158</v>
+        <v>78164</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2434,10 +2435,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>545290</v>
+        <v>545275</v>
       </c>
       <c r="R17" t="n">
-        <v>7206432</v>
+        <v>7206403</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2469,7 +2470,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2479,7 +2480,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2506,10 +2507,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113188922</v>
+        <v>113188925</v>
       </c>
       <c r="B18" t="n">
-        <v>78158</v>
+        <v>78164</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2546,10 +2547,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>545267</v>
+        <v>545248</v>
       </c>
       <c r="R18" t="n">
-        <v>7206397</v>
+        <v>7206407</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2581,7 +2582,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2591,7 +2592,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2618,10 +2619,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113188924</v>
+        <v>113188848</v>
       </c>
       <c r="B19" t="n">
-        <v>78158</v>
+        <v>74350</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2634,21 +2635,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>1467</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2658,10 +2659,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>545265</v>
+        <v>545291</v>
       </c>
       <c r="R19" t="n">
-        <v>7206396</v>
+        <v>7206429</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2693,7 +2694,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2703,7 +2704,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2730,10 +2731,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113188843</v>
+        <v>113188916</v>
       </c>
       <c r="B20" t="n">
-        <v>56785</v>
+        <v>78164</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2746,39 +2747,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>545262</v>
+        <v>545387</v>
       </c>
       <c r="R20" t="n">
-        <v>7206397</v>
+        <v>7206545</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2810,7 +2806,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2820,7 +2816,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2847,10 +2843,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113188920</v>
+        <v>113188852</v>
       </c>
       <c r="B21" t="n">
-        <v>78158</v>
+        <v>56880</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2859,38 +2855,42 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>545275</v>
+        <v>545348</v>
       </c>
       <c r="R21" t="n">
-        <v>7206403</v>
+        <v>7206503</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2922,7 +2922,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2932,7 +2932,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2959,10 +2959,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113188841</v>
+        <v>113188839</v>
       </c>
       <c r="B22" t="n">
-        <v>56914</v>
+        <v>56773</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2975,26 +2975,27 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3003,10 +3004,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>545269</v>
+        <v>545382</v>
       </c>
       <c r="R22" t="n">
-        <v>7206387</v>
+        <v>7206546</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3038,7 +3039,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3048,7 +3049,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3075,10 +3076,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113188838</v>
+        <v>113188924</v>
       </c>
       <c r="B23" t="n">
-        <v>56769</v>
+        <v>78164</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3091,39 +3092,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>545382</v>
+        <v>545265</v>
       </c>
       <c r="R23" t="n">
-        <v>7206578</v>
+        <v>7206396</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3155,7 +3151,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3165,7 +3161,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3192,10 +3188,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>113188853</v>
+        <v>113188835</v>
       </c>
       <c r="B24" t="n">
-        <v>78240</v>
+        <v>74345</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3208,21 +3204,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>864</v>
+        <v>6440</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3232,10 +3228,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>545268</v>
+        <v>545274</v>
       </c>
       <c r="R24" t="n">
-        <v>7206396</v>
+        <v>7206404</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3267,7 +3263,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3277,7 +3273,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3304,10 +3300,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>113188925</v>
+        <v>113188841</v>
       </c>
       <c r="B25" t="n">
-        <v>78158</v>
+        <v>56918</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3320,34 +3316,38 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>545248</v>
+        <v>545269</v>
       </c>
       <c r="R25" t="n">
-        <v>7206407</v>
+        <v>7206387</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3379,7 +3379,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3389,7 +3389,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3419,7 +3419,7 @@
         <v>113188917</v>
       </c>
       <c r="B26" t="n">
-        <v>78158</v>
+        <v>78164</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>

--- a/artfynd/A 48227-2023 artfynd.xlsx
+++ b/artfynd/A 48227-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 48227-2023 artfynd.xlsx
+++ b/artfynd/A 48227-2023 artfynd.xlsx
@@ -3528,10 +3528,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121072613</v>
+        <v>121072617</v>
       </c>
       <c r="B27" t="n">
-        <v>78598</v>
+        <v>91137</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3540,25 +3540,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3568,10 +3568,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>545245</v>
+        <v>545243</v>
       </c>
       <c r="R27" t="n">
-        <v>7206404</v>
+        <v>7206331</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3603,7 +3603,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3613,7 +3613,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3640,10 +3640,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121072608</v>
+        <v>121072610</v>
       </c>
       <c r="B28" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3680,10 +3680,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>545374</v>
+        <v>545331</v>
       </c>
       <c r="R28" t="n">
-        <v>7206592</v>
+        <v>7206507</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3715,7 +3715,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3725,7 +3725,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3752,10 +3752,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121072611</v>
+        <v>121072618</v>
       </c>
       <c r="B29" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3792,10 +3792,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>545237</v>
+        <v>545241</v>
       </c>
       <c r="R29" t="n">
-        <v>7206420</v>
+        <v>7206329</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3827,7 +3827,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3837,7 +3837,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3864,10 +3864,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121072617</v>
+        <v>121072619</v>
       </c>
       <c r="B30" t="n">
-        <v>91127</v>
+        <v>78601</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3876,25 +3876,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3904,10 +3904,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>545243</v>
+        <v>545241</v>
       </c>
       <c r="R30" t="n">
-        <v>7206331</v>
+        <v>7206332</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3939,7 +3939,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3949,7 +3949,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3976,10 +3976,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121072612</v>
+        <v>121072611</v>
       </c>
       <c r="B31" t="n">
-        <v>90701</v>
+        <v>78601</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3992,21 +3992,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4016,10 +4016,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>545241</v>
+        <v>545237</v>
       </c>
       <c r="R31" t="n">
-        <v>7206415</v>
+        <v>7206420</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4088,10 +4088,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121072610</v>
+        <v>121072613</v>
       </c>
       <c r="B32" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>545331</v>
+        <v>545245</v>
       </c>
       <c r="R32" t="n">
-        <v>7206507</v>
+        <v>7206404</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4163,7 +4163,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4173,7 +4173,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4200,10 +4200,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121072607</v>
+        <v>121072608</v>
       </c>
       <c r="B33" t="n">
-        <v>90705</v>
+        <v>78601</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4216,21 +4216,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4275,7 +4275,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4285,7 +4285,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4312,10 +4312,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121072616</v>
+        <v>121072607</v>
       </c>
       <c r="B34" t="n">
-        <v>90683</v>
+        <v>90715</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4328,21 +4328,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4352,10 +4352,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>545243</v>
+        <v>545374</v>
       </c>
       <c r="R34" t="n">
-        <v>7206332</v>
+        <v>7206592</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4387,7 +4387,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4397,7 +4397,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4427,7 +4427,7 @@
         <v>121072609</v>
       </c>
       <c r="B35" t="n">
-        <v>57348</v>
+        <v>57351</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4541,10 +4541,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121072619</v>
+        <v>121072616</v>
       </c>
       <c r="B36" t="n">
-        <v>78598</v>
+        <v>90693</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4557,21 +4557,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4581,7 +4581,7 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>545241</v>
+        <v>545243</v>
       </c>
       <c r="R36" t="n">
         <v>7206332</v>
@@ -4616,7 +4616,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4656,7 +4656,7 @@
         <v>121072615</v>
       </c>
       <c r="B37" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4765,10 +4765,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121072618</v>
+        <v>121072612</v>
       </c>
       <c r="B38" t="n">
-        <v>78598</v>
+        <v>90711</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4781,21 +4781,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4808,7 +4808,7 @@
         <v>545241</v>
       </c>
       <c r="R38" t="n">
-        <v>7206329</v>
+        <v>7206415</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4840,7 +4840,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4850,7 +4850,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="AD38" t="b">

--- a/artfynd/A 48227-2023 artfynd.xlsx
+++ b/artfynd/A 48227-2023 artfynd.xlsx
@@ -3528,10 +3528,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121072617</v>
+        <v>121072615</v>
       </c>
       <c r="B27" t="n">
-        <v>91137</v>
+        <v>78601</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3540,25 +3540,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3568,10 +3568,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>545243</v>
+        <v>545233</v>
       </c>
       <c r="R27" t="n">
-        <v>7206331</v>
+        <v>7206362</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3603,7 +3603,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>08:38</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3613,7 +3613,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>08:38</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3640,10 +3640,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121072610</v>
+        <v>121072616</v>
       </c>
       <c r="B28" t="n">
-        <v>78601</v>
+        <v>90693</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3656,21 +3656,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3680,10 +3680,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>545331</v>
+        <v>545243</v>
       </c>
       <c r="R28" t="n">
-        <v>7206507</v>
+        <v>7206332</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3715,7 +3715,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3725,7 +3725,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3752,10 +3752,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121072618</v>
+        <v>121072607</v>
       </c>
       <c r="B29" t="n">
-        <v>78601</v>
+        <v>90715</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3768,21 +3768,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3792,10 +3792,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>545241</v>
+        <v>545374</v>
       </c>
       <c r="R29" t="n">
-        <v>7206329</v>
+        <v>7206592</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3827,7 +3827,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3837,7 +3837,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3864,7 +3864,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121072619</v>
+        <v>121072618</v>
       </c>
       <c r="B30" t="n">
         <v>78601</v>
@@ -3907,7 +3907,7 @@
         <v>545241</v>
       </c>
       <c r="R30" t="n">
-        <v>7206332</v>
+        <v>7206329</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3939,7 +3939,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3949,7 +3949,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3976,7 +3976,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121072611</v>
+        <v>121072610</v>
       </c>
       <c r="B31" t="n">
         <v>78601</v>
@@ -4016,10 +4016,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>545237</v>
+        <v>545331</v>
       </c>
       <c r="R31" t="n">
-        <v>7206420</v>
+        <v>7206507</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4051,7 +4051,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4061,7 +4061,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4088,10 +4088,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121072613</v>
+        <v>121072609</v>
       </c>
       <c r="B32" t="n">
-        <v>78601</v>
+        <v>57351</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4104,34 +4104,39 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>545245</v>
+        <v>545327</v>
       </c>
       <c r="R32" t="n">
-        <v>7206404</v>
+        <v>7206509</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4163,7 +4168,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4173,7 +4178,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4200,7 +4205,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121072608</v>
+        <v>121072611</v>
       </c>
       <c r="B33" t="n">
         <v>78601</v>
@@ -4240,10 +4245,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>545374</v>
+        <v>545237</v>
       </c>
       <c r="R33" t="n">
-        <v>7206592</v>
+        <v>7206420</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4275,7 +4280,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4285,7 +4290,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4312,10 +4317,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121072607</v>
+        <v>121072608</v>
       </c>
       <c r="B34" t="n">
-        <v>90715</v>
+        <v>78601</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4328,21 +4333,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4387,7 +4392,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4397,7 +4402,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4424,10 +4429,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121072609</v>
+        <v>121072612</v>
       </c>
       <c r="B35" t="n">
-        <v>57351</v>
+        <v>90711</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4440,39 +4445,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>545327</v>
+        <v>545241</v>
       </c>
       <c r="R35" t="n">
-        <v>7206509</v>
+        <v>7206415</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4504,7 +4504,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4514,7 +4514,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4541,10 +4541,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121072616</v>
+        <v>121072613</v>
       </c>
       <c r="B36" t="n">
-        <v>90693</v>
+        <v>78601</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4557,21 +4557,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4581,10 +4581,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>545243</v>
+        <v>545245</v>
       </c>
       <c r="R36" t="n">
-        <v>7206332</v>
+        <v>7206404</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4616,7 +4616,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4653,7 +4653,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121072615</v>
+        <v>121072619</v>
       </c>
       <c r="B37" t="n">
         <v>78601</v>
@@ -4693,10 +4693,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>545233</v>
+        <v>545241</v>
       </c>
       <c r="R37" t="n">
-        <v>7206362</v>
+        <v>7206332</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4728,7 +4728,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>08:38</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4738,7 +4738,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>08:38</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4765,10 +4765,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121072612</v>
+        <v>121072617</v>
       </c>
       <c r="B38" t="n">
-        <v>90711</v>
+        <v>91137</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4777,25 +4777,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1204</v>
+        <v>1209</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4805,10 +4805,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>545241</v>
+        <v>545243</v>
       </c>
       <c r="R38" t="n">
-        <v>7206415</v>
+        <v>7206331</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4840,7 +4840,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4850,7 +4850,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="AD38" t="b">

--- a/artfynd/A 48227-2023 artfynd.xlsx
+++ b/artfynd/A 48227-2023 artfynd.xlsx
@@ -3531,7 +3531,7 @@
         <v>121072615</v>
       </c>
       <c r="B27" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3640,10 +3640,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121072616</v>
+        <v>121072608</v>
       </c>
       <c r="B28" t="n">
-        <v>90693</v>
+        <v>78604</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3656,21 +3656,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3680,10 +3680,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>545243</v>
+        <v>545374</v>
       </c>
       <c r="R28" t="n">
-        <v>7206332</v>
+        <v>7206592</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3715,7 +3715,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3725,7 +3725,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3752,10 +3752,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121072607</v>
+        <v>121072610</v>
       </c>
       <c r="B29" t="n">
-        <v>90715</v>
+        <v>78604</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3768,21 +3768,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3792,10 +3792,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>545374</v>
+        <v>545331</v>
       </c>
       <c r="R29" t="n">
-        <v>7206592</v>
+        <v>7206507</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3827,7 +3827,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3837,7 +3837,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3864,10 +3864,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121072618</v>
+        <v>121072619</v>
       </c>
       <c r="B30" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3907,7 +3907,7 @@
         <v>545241</v>
       </c>
       <c r="R30" t="n">
-        <v>7206329</v>
+        <v>7206332</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3939,7 +3939,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3949,7 +3949,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3976,10 +3976,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121072610</v>
+        <v>121072618</v>
       </c>
       <c r="B31" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4016,10 +4016,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>545331</v>
+        <v>545241</v>
       </c>
       <c r="R31" t="n">
-        <v>7206507</v>
+        <v>7206329</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4051,7 +4051,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4061,7 +4061,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4088,10 +4088,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121072609</v>
+        <v>121072617</v>
       </c>
       <c r="B32" t="n">
-        <v>57351</v>
+        <v>91149</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4100,43 +4100,38 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>545327</v>
+        <v>545243</v>
       </c>
       <c r="R32" t="n">
-        <v>7206509</v>
+        <v>7206331</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4168,7 +4163,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4178,7 +4173,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4205,10 +4200,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121072611</v>
+        <v>121072613</v>
       </c>
       <c r="B33" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4245,10 +4240,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>545237</v>
+        <v>545245</v>
       </c>
       <c r="R33" t="n">
-        <v>7206420</v>
+        <v>7206404</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4317,10 +4312,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121072608</v>
+        <v>121072616</v>
       </c>
       <c r="B34" t="n">
-        <v>78601</v>
+        <v>90705</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4333,21 +4328,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4357,10 +4352,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>545374</v>
+        <v>545243</v>
       </c>
       <c r="R34" t="n">
-        <v>7206592</v>
+        <v>7206332</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4392,7 +4387,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4402,7 +4397,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4432,7 +4427,7 @@
         <v>121072612</v>
       </c>
       <c r="B35" t="n">
-        <v>90711</v>
+        <v>90723</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4541,10 +4536,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121072613</v>
+        <v>121072611</v>
       </c>
       <c r="B36" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4581,10 +4576,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>545245</v>
+        <v>545237</v>
       </c>
       <c r="R36" t="n">
-        <v>7206404</v>
+        <v>7206420</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4653,10 +4648,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121072619</v>
+        <v>121072607</v>
       </c>
       <c r="B37" t="n">
-        <v>78601</v>
+        <v>90727</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4669,21 +4664,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4693,10 +4688,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>545241</v>
+        <v>545374</v>
       </c>
       <c r="R37" t="n">
-        <v>7206332</v>
+        <v>7206592</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4728,7 +4723,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4738,7 +4733,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4765,10 +4760,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121072617</v>
+        <v>121072609</v>
       </c>
       <c r="B38" t="n">
-        <v>91137</v>
+        <v>57351</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4777,38 +4772,43 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>545243</v>
+        <v>545327</v>
       </c>
       <c r="R38" t="n">
-        <v>7206331</v>
+        <v>7206509</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4840,7 +4840,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4850,7 +4850,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AD38" t="b">
